--- a/docs and files/Tax 26/Book1.xlsx
+++ b/docs and files/Tax 26/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kayesh\Desktop\Tax 26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DevKayesh\Users\kayesh\source\repos\app-sales\docs and files\Tax 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:0_{E2AFE761-6324-4D90-B944-C95B49B8C688}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD34367F-54F8-4C0D-A504-69FF0C1E30DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{5532516C-4457-4313-89DF-0CE26A5B2D3A}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="151">
   <si>
     <t>3021256950007</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>ENVATO PTY LTD</t>
-  </si>
-  <si>
-    <t>Page 4</t>
   </si>
   <si>
     <t xml:space="preserve">Deposit Pension Scheme (DPS) </t>
@@ -369,6 +366,120 @@
   </si>
   <si>
     <t>Sonali Bank, Gulshan New North Circle</t>
+  </si>
+  <si>
+    <t>1133580000303936</t>
+  </si>
+  <si>
+    <t>1133581000002676</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>INTEREST ON FIXED DEPOSIT ( INT RATE: %)</t>
+  </si>
+  <si>
+    <t>TAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTEREST ON FIXED DEPOSIT </t>
+  </si>
+  <si>
+    <t>INTEREST ON FIXED DEPOSIT</t>
+  </si>
+  <si>
+    <t>DEPOSIT MATURITY</t>
+  </si>
+  <si>
+    <t>INSTALLMENT/NEW DEPOSIT AND CREDIT INTEREST</t>
+  </si>
+  <si>
+    <t>Opening</t>
+  </si>
+  <si>
+    <t>DPS - 5000 BDT</t>
+  </si>
+  <si>
+    <t>DPS - 3000 BDT</t>
+  </si>
+  <si>
+    <t>FDR - 1L BDT</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Rebate</t>
+  </si>
+  <si>
+    <t>Page 4.2</t>
+  </si>
+  <si>
+    <t>Page 4.1</t>
+  </si>
+  <si>
+    <t>Total Source TAX</t>
+  </si>
+  <si>
+    <t>Gross Wealth</t>
+  </si>
+  <si>
+    <t>NW Previous Income Year</t>
+  </si>
+  <si>
+    <t>Change NW</t>
+  </si>
+  <si>
+    <t>Fund Flow IY</t>
+  </si>
+  <si>
+    <t>Total Fund Outflow</t>
+  </si>
+  <si>
+    <t>Source Fund</t>
+  </si>
+  <si>
+    <t>1/3rd</t>
+  </si>
+  <si>
+    <t>Taxable</t>
+  </si>
+  <si>
+    <t>Allow Investment 10%</t>
+  </si>
+  <si>
+    <t>Nill</t>
+  </si>
+  <si>
+    <t>3L</t>
+  </si>
+  <si>
+    <t>4L</t>
+  </si>
+  <si>
+    <t>Net TAX</t>
+  </si>
+  <si>
+    <t>Investment Rebate</t>
+  </si>
+  <si>
+    <t>Payble TAX</t>
+  </si>
+  <si>
+    <t>Salary TDS</t>
+  </si>
+  <si>
+    <t>Bank TDS</t>
+  </si>
+  <si>
+    <t>Incentive</t>
+  </si>
+  <si>
+    <t>Outstanding TAX</t>
   </si>
 </sst>
 </file>
@@ -376,9 +487,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$-5000445]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$-5000445]#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,8 +505,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +561,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -457,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -481,10 +604,17 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1092,17 +1222,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C91374D-A718-41F3-94CD-41CBFD607B49}">
-  <dimension ref="B2:J62"/>
+  <dimension ref="B2:J112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="61.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1161,7 +1291,7 @@
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="22" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1324,16 +1454,16 @@
       <c r="F19" s="12">
         <v>1311</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>87</v>
-      </c>
       <c r="I19" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="22">
+        <v>112</v>
+      </c>
+      <c r="J19" s="21">
         <v>1291962</v>
       </c>
     </row>
@@ -1346,16 +1476,16 @@
       <c r="F20" s="12">
         <v>1311</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="I20" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="22">
+        <v>112</v>
+      </c>
+      <c r="J20" s="21">
         <v>1253383</v>
       </c>
     </row>
@@ -1368,16 +1498,16 @@
       <c r="F21" s="12">
         <v>1543</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>91</v>
-      </c>
       <c r="I21" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="22">
+        <v>112</v>
+      </c>
+      <c r="J21" s="21">
         <v>1253259</v>
       </c>
     </row>
@@ -1388,16 +1518,16 @@
       <c r="F22" s="12">
         <v>1543</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>93</v>
-      </c>
       <c r="I22" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J22" s="22">
+        <v>111</v>
+      </c>
+      <c r="J22" s="21">
         <v>1253676</v>
       </c>
     </row>
@@ -1410,16 +1540,16 @@
       <c r="F23" s="12">
         <v>1543</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>95</v>
-      </c>
       <c r="I23" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J23" s="22">
+        <v>111</v>
+      </c>
+      <c r="J23" s="21">
         <v>1282553</v>
       </c>
     </row>
@@ -1434,16 +1564,16 @@
       <c r="F24" s="12">
         <v>1543</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="I24" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J24" s="22">
+        <v>111</v>
+      </c>
+      <c r="J24" s="21">
         <v>1283267</v>
       </c>
     </row>
@@ -1458,16 +1588,16 @@
       <c r="F25" s="12">
         <v>1543</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="H25" s="12" t="s">
-        <v>99</v>
-      </c>
       <c r="I25" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J25" s="22">
+        <v>111</v>
+      </c>
+      <c r="J25" s="21">
         <v>1286025</v>
       </c>
     </row>
@@ -1482,16 +1612,16 @@
       <c r="F26" s="12">
         <v>1543</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="H26" s="12" t="s">
-        <v>101</v>
-      </c>
       <c r="I26" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J26" s="22">
+        <v>111</v>
+      </c>
+      <c r="J26" s="21">
         <v>1281025</v>
       </c>
     </row>
@@ -1506,16 +1636,16 @@
       <c r="F27" s="12">
         <v>1543</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="H27" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="I27" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J27" s="22">
+        <v>111</v>
+      </c>
+      <c r="J27" s="21">
         <v>1279445</v>
       </c>
     </row>
@@ -1530,16 +1660,16 @@
       <c r="F28" s="12">
         <v>1543</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H28" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="I28" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J28" s="22">
+        <v>111</v>
+      </c>
+      <c r="J28" s="21">
         <v>1292789</v>
       </c>
     </row>
@@ -1555,15 +1685,15 @@
         <v>1543</v>
       </c>
       <c r="G29" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H29" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="I29" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J29" s="22">
+        <v>111</v>
+      </c>
+      <c r="J29" s="21">
         <v>1262294</v>
       </c>
     </row>
@@ -1575,15 +1705,15 @@
         <v>1543</v>
       </c>
       <c r="G30" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="I30" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J30" s="22">
+      <c r="J30" s="21">
         <v>1254674</v>
       </c>
     </row>
@@ -1599,7 +1729,7 @@
         <v>18052</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
@@ -1725,31 +1855,29 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C39" s="13"/>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="13">
-        <v>8969</v>
-      </c>
-      <c r="G39" s="13">
+      <c r="F39" s="28">
+        <v>10250</v>
+      </c>
+      <c r="G39" s="28">
         <v>0</v>
       </c>
-      <c r="H39" s="13">
-        <v>0</v>
-      </c>
-      <c r="I39" s="13">
+      <c r="H39" s="28">
+        <v>1281</v>
+      </c>
+      <c r="I39" s="28">
         <v>100000</v>
       </c>
       <c r="J39" s="13"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C40" s="13"/>
-      <c r="D40" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -1757,45 +1885,61 @@
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
     </row>
-    <row r="43" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C43" s="15" t="s">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E41" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="20">
+        <f>SUM(F35:F40)</f>
+        <v>20926</v>
+      </c>
+      <c r="G41" s="12"/>
+      <c r="H41" s="20">
+        <f>SUM(H35:H40)</f>
+        <v>2367</v>
+      </c>
+      <c r="I41" s="20">
+        <f>SUM(I35:I40)</f>
+        <v>330234</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E42" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" s="20"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="20">
+        <f>H41+F31</f>
+        <v>20419</v>
+      </c>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="44" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="C44" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="17">
+      <c r="D44" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="17">
         <v>13212.97</v>
       </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C46" s="18"/>
-      <c r="D46" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>68</v>
-      </c>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
       <c r="F46" s="18"/>
       <c r="G46" s="18"/>
       <c r="H46" s="18"/>
@@ -1803,14 +1947,12 @@
       <c r="J46" s="18"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C47" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="18">
-        <v>40000</v>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="F47" s="18"/>
       <c r="G47" s="18"/>
@@ -1819,9 +1961,15 @@
       <c r="J47" s="18"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="C48" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="18">
+        <v>40000</v>
+      </c>
       <c r="F48" s="18"/>
       <c r="G48" s="18"/>
       <c r="H48" s="18"/>
@@ -1829,9 +1977,7 @@
       <c r="J48" s="18"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="18" t="s">
-        <v>69</v>
-      </c>
+      <c r="C49" s="18"/>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
@@ -1841,13 +1987,11 @@
       <c r="J49" s="18"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C50" s="18"/>
-      <c r="D50" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>72</v>
-      </c>
+      <c r="C50" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="18"/>
       <c r="H50" s="18"/>
@@ -1855,14 +1999,12 @@
       <c r="J50" s="18"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="18"/>
+      <c r="D51" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D51" s="18">
-        <v>28050</v>
-      </c>
-      <c r="E51" s="18">
-        <v>28050</v>
+      <c r="E51" s="18" t="s">
+        <v>71</v>
       </c>
       <c r="F51" s="18"/>
       <c r="G51" s="18"/>
@@ -1870,219 +2012,921 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9" t="s">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C52" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="18">
+        <v>28050</v>
+      </c>
+      <c r="E52" s="18">
+        <v>28050</v>
+      </c>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="G54" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="H54" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D54" s="9">
-        <f>H54</f>
-        <v>156600</v>
-      </c>
-      <c r="E54" s="9">
-        <f>F54/12</f>
-        <v>12000</v>
-      </c>
-      <c r="F54" s="9">
-        <v>144000</v>
-      </c>
-      <c r="G54" s="9">
-        <v>13050</v>
-      </c>
-      <c r="H54" s="9">
-        <f>G54*12</f>
-        <v>156600</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" s="9">
-        <f t="shared" ref="D55:D59" si="0">H55</f>
-        <v>78000</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D55" s="9"/>
       <c r="E55" s="9">
-        <f t="shared" ref="E55:E59" si="1">F55/12</f>
-        <v>6500</v>
+        <f>F55/12</f>
+        <v>12000</v>
       </c>
       <c r="F55" s="9">
-        <v>78000</v>
+        <v>144000</v>
       </c>
       <c r="G55" s="9">
-        <v>6500</v>
+        <v>13050</v>
       </c>
       <c r="H55" s="9">
         <f>G55*12</f>
-        <v>78000</v>
+        <v>156600</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C56" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" s="9">
-        <f t="shared" si="0"/>
-        <v>9600</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D56" s="9"/>
       <c r="E56" s="9">
-        <f t="shared" si="1"/>
-        <v>725</v>
+        <f t="shared" ref="E56:E60" si="0">F56/12</f>
+        <v>6500</v>
       </c>
       <c r="F56" s="9">
-        <v>8700</v>
+        <v>78000</v>
       </c>
       <c r="G56" s="9">
-        <v>800</v>
+        <v>6500</v>
       </c>
       <c r="H56" s="9">
-        <f>G56*12</f>
-        <v>9600</v>
+        <f t="shared" ref="H56:H60" si="1">G56*12</f>
+        <v>78000</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="9"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C57" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="9">
+        <v>75</v>
+      </c>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9">
         <f t="shared" si="0"/>
-        <v>14160</v>
-      </c>
-      <c r="E57" s="9">
+        <v>725</v>
+      </c>
+      <c r="F57" s="9">
+        <v>8700</v>
+      </c>
+      <c r="G57" s="9">
+        <v>800</v>
+      </c>
+      <c r="H57" s="9">
         <f t="shared" si="1"/>
-        <v>1180</v>
-      </c>
-      <c r="F57" s="9">
-        <v>14160</v>
-      </c>
-      <c r="G57" s="9">
-        <v>1180</v>
-      </c>
-      <c r="H57" s="9">
-        <f>G57*12</f>
-        <v>14160</v>
+        <v>9600</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C58" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="9">
+        <v>76</v>
+      </c>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9">
         <f t="shared" si="0"/>
-        <v>7560</v>
-      </c>
-      <c r="E58" s="9">
+        <v>1180</v>
+      </c>
+      <c r="F58" s="9">
+        <v>14160</v>
+      </c>
+      <c r="G58" s="9">
+        <v>1180</v>
+      </c>
+      <c r="H58" s="9">
         <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="F58" s="9">
-        <v>7200</v>
-      </c>
-      <c r="G58" s="9">
-        <v>630</v>
-      </c>
-      <c r="H58" s="9">
-        <f>G58*12</f>
-        <v>7560</v>
+        <v>14160</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="9"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C59" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="9">
+        <v>77</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9">
         <f t="shared" si="0"/>
-        <v>15600</v>
-      </c>
-      <c r="E59" s="9">
+        <v>600</v>
+      </c>
+      <c r="F59" s="9">
+        <v>7200</v>
+      </c>
+      <c r="G59" s="9">
+        <v>630</v>
+      </c>
+      <c r="H59" s="9">
         <f t="shared" si="1"/>
-        <v>1250</v>
-      </c>
-      <c r="F59" s="9">
-        <v>15000</v>
-      </c>
-      <c r="G59" s="9">
-        <v>1300</v>
-      </c>
-      <c r="H59" s="9">
-        <f>G59*12</f>
-        <v>15600</v>
+        <v>7560</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="9"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C60" s="9"/>
+      <c r="C60" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
+      <c r="E60" s="9">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="F60" s="9">
+        <v>15000</v>
+      </c>
+      <c r="G60" s="9">
+        <v>1300</v>
+      </c>
+      <c r="H60" s="9">
+        <f t="shared" si="1"/>
+        <v>15600</v>
+      </c>
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C61" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D61" s="9">
-        <v>1085</v>
-      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="9"/>
-      <c r="F61" s="9">
-        <v>6698</v>
-      </c>
+      <c r="F61" s="9"/>
       <c r="G61" s="9"/>
-      <c r="H61" s="9">
-        <v>5500</v>
-      </c>
+      <c r="H61" s="9"/>
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C62" s="9"/>
+      <c r="C62" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9" t="s">
-        <v>85</v>
-      </c>
+      <c r="F62" s="9">
+        <v>6698</v>
+      </c>
+      <c r="G62" s="9"/>
       <c r="H62" s="9">
-        <f>SUM(H54:H61)</f>
-        <v>287020</v>
+        <f>H42</f>
+        <v>20419</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="20">
+        <f>SUM(F55:F62)</f>
+        <v>273758</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H63" s="20">
+        <f>SUM(H55:H62)</f>
+        <v>301939</v>
+      </c>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E66" s="23">
+        <v>47150</v>
+      </c>
+      <c r="F66" s="23">
+        <v>46054</v>
+      </c>
+      <c r="G66" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C67" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E67" s="23">
+        <v>46054</v>
+      </c>
+      <c r="F67" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G67" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H67" s="13">
+        <v>24.38</v>
+      </c>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C68" s="14"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23">
+        <v>46113</v>
+      </c>
+      <c r="G68" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H68" s="13">
+        <v>48.95</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C69" s="14"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23">
+        <v>46144</v>
+      </c>
+      <c r="G69" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H69" s="13">
+        <v>73.72</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C70" s="14"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23">
+        <v>46174</v>
+      </c>
+      <c r="G70" s="13">
+        <v>3000</v>
+      </c>
+      <c r="H70" s="13">
+        <v>98.69</v>
+      </c>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C71" s="14"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G71" s="24">
+        <f>SUM(G66:G70)</f>
+        <v>15000</v>
+      </c>
+      <c r="H71" s="24">
+        <f>SUM(H66:H70)</f>
+        <v>245.74</v>
+      </c>
+      <c r="I71" s="24">
+        <f>G71+H71</f>
+        <v>15245.74</v>
+      </c>
+      <c r="J71" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C72" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="23">
+        <v>46510</v>
+      </c>
+      <c r="F72" s="23">
+        <v>45964</v>
+      </c>
+      <c r="G72" s="13">
+        <v>5125</v>
+      </c>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J72" s="13"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C73" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E73" s="23">
+        <v>45780</v>
+      </c>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13">
+        <v>512.5</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C74" s="14"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13">
+        <v>4612.5</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C75" s="14"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23">
+        <v>46145</v>
+      </c>
+      <c r="G75" s="13">
+        <v>5125</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C76" s="14"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13">
+        <v>768.75</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C77" s="14"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13">
+        <v>4356.25</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C78" s="14"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G78" s="24">
+        <f>G72+G75</f>
+        <v>10250</v>
+      </c>
+      <c r="H78" s="24">
+        <f>H77+H74</f>
+        <v>8968.75</v>
+      </c>
+      <c r="I78" s="24">
+        <f>H76+H73</f>
+        <v>1281.25</v>
+      </c>
+      <c r="J78" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C79" s="14"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23">
+        <v>46145</v>
+      </c>
+      <c r="G79" s="13">
+        <v>10000</v>
+      </c>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C80" s="14"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13">
+        <v>10000</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J80" s="13"/>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C81" s="14"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+    </row>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C82" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="23">
+        <v>47435</v>
+      </c>
+      <c r="F82" s="23">
+        <v>45851</v>
+      </c>
+      <c r="G82" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H82" s="13">
+        <v>341.74</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J82" s="13"/>
+    </row>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C83" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E83" s="23">
+        <v>45609</v>
+      </c>
+      <c r="F83" s="23">
+        <v>45882</v>
+      </c>
+      <c r="G83" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H83" s="13">
+        <v>387.72</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J83" s="13"/>
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="23">
+        <v>45913</v>
+      </c>
+      <c r="G84" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H84" s="13">
+        <v>432.62</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J84" s="13"/>
+    </row>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="23">
+        <v>45943</v>
+      </c>
+      <c r="G85" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H85" s="13">
+        <v>477.89</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J85" s="13"/>
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="23">
+        <v>45974</v>
+      </c>
+      <c r="G86" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H86" s="13">
+        <v>523.54</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="23">
+        <v>46004</v>
+      </c>
+      <c r="G87" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H87" s="13">
+        <v>569.57000000000005</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="23">
+        <v>46035</v>
+      </c>
+      <c r="G88" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H88" s="13">
+        <v>615.98</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="23">
+        <v>46067</v>
+      </c>
+      <c r="G89" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H89" s="13">
+        <v>662.78</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="23">
+        <v>46095</v>
+      </c>
+      <c r="G90" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H90" s="13">
+        <v>709.97</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J90" s="13"/>
+    </row>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="23">
+        <v>46125</v>
+      </c>
+      <c r="G91" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H91" s="13">
+        <v>757.56</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J91" s="13"/>
+    </row>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="23">
+        <v>46155</v>
+      </c>
+      <c r="G92" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H92" s="13">
+        <v>805.54</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J92" s="13"/>
+    </row>
+    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="23">
+        <v>46186</v>
+      </c>
+      <c r="G93" s="13">
+        <v>5000</v>
+      </c>
+      <c r="H93" s="13">
+        <v>853.91</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G94" s="24">
+        <f>SUM(G82:G93)</f>
+        <v>60000</v>
+      </c>
+      <c r="H94" s="24">
+        <f>SUM(H82:H93)</f>
+        <v>7138.8200000000006</v>
+      </c>
+      <c r="I94" s="24">
+        <f>G94+H94</f>
+        <v>67138.820000000007</v>
+      </c>
+      <c r="J94" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>116</v>
+      </c>
+      <c r="E98">
+        <f>E31</f>
+        <v>1150050</v>
+      </c>
+    </row>
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D99" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E99">
+        <f>E98/3</f>
+        <v>383350</v>
+      </c>
+    </row>
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100">
+        <f>E98-E99</f>
+        <v>766700</v>
+      </c>
+      <c r="G100">
+        <f>SUM(G102:G104)</f>
+        <v>787626</v>
+      </c>
+    </row>
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>140</v>
+      </c>
+      <c r="E101">
+        <f>E100*0.1</f>
+        <v>76670</v>
+      </c>
+    </row>
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F102" t="s">
+        <v>141</v>
+      </c>
+      <c r="G102">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F103" t="s">
+        <v>142</v>
+      </c>
+      <c r="G103">
+        <v>300000</v>
+      </c>
+      <c r="H103">
+        <f>G103*0.1</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F104" t="s">
+        <v>143</v>
+      </c>
+      <c r="G104">
+        <f>E100-(G102+G103) + 20926</f>
+        <v>87626</v>
+      </c>
+      <c r="H104">
+        <f>G104*0.15</f>
+        <v>13143.9</v>
+      </c>
+    </row>
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H105">
+        <f>H103+H104</f>
+        <v>43143.9</v>
+      </c>
+      <c r="I105" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>132</v>
+      </c>
+      <c r="E106">
+        <v>2137063</v>
+      </c>
+      <c r="H106">
+        <v>17110</v>
+      </c>
+      <c r="I106" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>133</v>
+      </c>
+      <c r="E107">
+        <v>1268026</v>
+      </c>
+      <c r="H107">
+        <f>H105-H106</f>
+        <v>26033.9</v>
+      </c>
+      <c r="I107" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>134</v>
+      </c>
+      <c r="E108">
+        <f>E106-E107</f>
+        <v>869037</v>
+      </c>
+      <c r="H108">
+        <v>18052</v>
+      </c>
+      <c r="I108" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H109">
+        <v>2367</v>
+      </c>
+      <c r="I109" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>135</v>
+      </c>
+      <c r="E110">
+        <v>301939</v>
+      </c>
+      <c r="H110">
+        <v>281</v>
+      </c>
+      <c r="I110" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>136</v>
+      </c>
+      <c r="E111">
+        <f>E108+E110</f>
+        <v>1170976</v>
+      </c>
+      <c r="H111">
+        <f>H107-(H108+H109+H110)</f>
+        <v>5333.9000000000015</v>
+      </c>
+      <c r="I111" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>137</v>
+      </c>
+      <c r="E112">
+        <v>1170976</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
